--- a/artfynd/A 45224-2024 artfynd.xlsx
+++ b/artfynd/A 45224-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ25"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4899152</v>
+        <v>137527950</v>
       </c>
       <c r="B4" t="n">
-        <v>100143</v>
+        <v>108480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,34 +923,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222467</v>
+        <v>220083</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+          <t>Slåttmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500163</v>
+        <v>500185</v>
       </c>
       <c r="R4" t="n">
-        <v>7026264</v>
+        <v>7026360</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,11 +985,6 @@
           <t>2012-09-10</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>rikkärrskant</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -998,16 +993,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Tallskog - barrblandskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bodil Carlsson</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1017,21 +1007,21 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Åtgärdsprogram för hotade arter</t>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4899152</t>
+          <t>https://artportalen.se/Sighting/137527950</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6776533</v>
+        <v>137527932</v>
       </c>
       <c r="B5" t="n">
-        <v>99024</v>
+        <v>110427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,34 +1029,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>504</v>
+        <v>220294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+          <t>Slåttmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500735</v>
+        <v>500162</v>
       </c>
       <c r="R5" t="n">
-        <v>7026456</v>
+        <v>7026263</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1093,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>6 bestånd, totalt ca 50 pl. inom ca 100 m2.</t>
+          <t>rikkärrskant</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,7 +1108,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bodil Carlsson</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1128,21 +1118,21 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Åtgärdsprogram för hotade arter</t>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6776533</t>
+          <t>https://artportalen.se/Sighting/137527932</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6776534</v>
+        <v>137527869</v>
       </c>
       <c r="B6" t="n">
-        <v>99024</v>
+        <v>106628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,16 +1140,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>504</v>
+        <v>221157</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1170,14 +1160,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+          <t>Slåttmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500743</v>
+        <v>500200</v>
       </c>
       <c r="R6" t="n">
-        <v>7026479</v>
+        <v>7026347</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,11 +1202,6 @@
           <t>2012-09-10</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>några plantor i rikkärrskant</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1229,7 +1214,7 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bodil Carlsson</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -1239,21 +1224,21 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Åtgärdsprogram för hotade arter</t>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6776534</t>
+          <t>https://artportalen.se/Sighting/137527869</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6776535</v>
+        <v>4899152</v>
       </c>
       <c r="B7" t="n">
-        <v>99024</v>
+        <v>100143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>504</v>
+        <v>222467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500736</v>
+        <v>500163</v>
       </c>
       <c r="R7" t="n">
-        <v>7026499</v>
+        <v>7026264</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1310,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 best. ca 10 pl.</t>
+          <t>rikkärrskant</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,6 +1321,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Tallskog - barrblandskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1355,16 +1345,16 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6776535</t>
+          <t>https://artportalen.se/Sighting/4899152</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6776536</v>
+        <v>137527930</v>
       </c>
       <c r="B8" t="n">
-        <v>99024</v>
+        <v>100465</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,34 +1362,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>504</v>
+        <v>222467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+          <t>Slåttmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500732</v>
+        <v>500162</v>
       </c>
       <c r="R8" t="n">
-        <v>7026498</v>
+        <v>7026263</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1426,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 best. ca 10 pl.</t>
+          <t>rikkärrskant</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,7 +1441,7 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bodil Carlsson</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1461,21 +1451,21 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Åtgärdsprogram för hotade arter</t>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6776536</t>
+          <t>https://artportalen.se/Sighting/137527930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1161247</v>
+        <v>6776533</v>
       </c>
       <c r="B9" t="n">
-        <v>91680</v>
+        <v>99024</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1483,21 +1473,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>504</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500734</v>
+        <v>500735</v>
       </c>
       <c r="R9" t="n">
-        <v>7026503</v>
+        <v>7026456</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,6 +1535,11 @@
           <t>2012-09-10</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>6 bestånd, totalt ca 50 pl. inom ca 100 m2.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1553,11 +1548,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Blandsumpskog - rikkärr</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1577,16 +1567,16 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1161247</t>
+          <t>https://artportalen.se/Sighting/6776533</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1208310</v>
+        <v>6776534</v>
       </c>
       <c r="B10" t="n">
-        <v>87412</v>
+        <v>99024</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,19 +1584,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3624</v>
+        <v>504</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1614,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500422</v>
+        <v>500743</v>
       </c>
       <c r="R10" t="n">
-        <v>7026184</v>
+        <v>7026479</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,6 +1646,11 @@
           <t>2012-09-10</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>några plantor i rikkärrskant</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1660,11 +1659,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Tallskog - barrblandskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1684,16 +1678,16 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1208310</t>
+          <t>https://artportalen.se/Sighting/6776534</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1208311</v>
+        <v>6776535</v>
       </c>
       <c r="B11" t="n">
-        <v>87412</v>
+        <v>99024</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,19 +1695,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3624</v>
+        <v>504</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1721,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500435</v>
+        <v>500736</v>
       </c>
       <c r="R11" t="n">
-        <v>7026139</v>
+        <v>7026499</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,6 +1757,11 @@
           <t>2012-09-10</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1 best. ca 10 pl.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1767,11 +1770,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Tallskog - barrblandskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1791,16 +1789,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1208311</t>
+          <t>https://artportalen.se/Sighting/6776535</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1256195</v>
+        <v>6776536</v>
       </c>
       <c r="B12" t="n">
-        <v>89035</v>
+        <v>99024</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,19 +1806,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4398</v>
+        <v>504</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitvaxing agg.</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1828,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500716</v>
+        <v>500732</v>
       </c>
       <c r="R12" t="n">
-        <v>7026420</v>
+        <v>7026498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,7 +1870,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>äldre skogsbilvägskant, vid liten bäck</t>
+          <t>1 best. ca 10 pl.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1879,11 +1881,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Tallskog - barrblandskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1903,54 +1900,54 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1256195</t>
+          <t>https://artportalen.se/Sighting/6776536</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1869486</v>
+        <v>137527986</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>99344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+          <t>Slåttmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500519</v>
+        <v>500731</v>
       </c>
       <c r="R13" t="n">
-        <v>7026330</v>
+        <v>7026498</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1984,7 +1981,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sparsamt på ett par granar</t>
+          <t>1 best. ca 10 pl.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1995,16 +1992,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Tallskog - barrblandskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bodil Carlsson</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -2014,59 +2006,59 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Åtgärdsprogram för hotade arter</t>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1869486</t>
+          <t>https://artportalen.se/Sighting/137527986</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1869487</v>
+        <v>137527987</v>
       </c>
       <c r="B14" t="n">
-        <v>79327</v>
+        <v>99344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+          <t>Slåttmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>500735</v>
       </c>
       <c r="R14" t="n">
-        <v>7026456</v>
+        <v>7026499</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2100,7 +2092,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sparsamt</t>
+          <t>1 best. ca 10 pl.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2111,16 +2103,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Blandsumpskog - rikkärr</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bodil Carlsson</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2130,61 +2117,56 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Åtgärdsprogram för hotade arter</t>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1869487</t>
+          <t>https://artportalen.se/Sighting/137527987</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115229281</v>
+        <v>137527988</v>
       </c>
       <c r="B15" t="n">
-        <v>57953</v>
+        <v>99344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>504</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Slåttmyren, Slåttmyren, Jmt</t>
+          <t>Slåttmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>501010</v>
+        <v>500742</v>
       </c>
       <c r="R15" t="n">
-        <v>7026103</v>
+        <v>7026479</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,17 +2193,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>några plantor i rikkärrskant</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,67 +2218,66 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115229281</t>
+          <t>https://artportalen.se/Sighting/137527988</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115229440</v>
+        <v>137527926</v>
       </c>
       <c r="B16" t="n">
-        <v>57953</v>
+        <v>96650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2812</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Slåttmyren, Slåttmyren, Jmt</t>
+          <t>Slåttmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501041</v>
+        <v>500359</v>
       </c>
       <c r="R16" t="n">
-        <v>7026164</v>
+        <v>7026366</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2323,12 +2304,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>vid Källbäcken</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,67 +2329,66 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115229440</t>
+          <t>https://artportalen.se/Sighting/137527926</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115229743</v>
+        <v>1161247</v>
       </c>
       <c r="B17" t="n">
-        <v>57953</v>
+        <v>91680</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slåttmyren, Slåttmyren, Jmt</t>
+          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500980</v>
+        <v>500734</v>
       </c>
       <c r="R17" t="n">
-        <v>7026149</v>
+        <v>7026503</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2430,12 +2415,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2446,31 +2431,40 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Blandsumpskog - rikkärr</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Bodil Carlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115229743</t>
+          <t>https://artportalen.se/Sighting/1161247</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115230124</v>
+        <v>1208310</v>
       </c>
       <c r="B18" t="n">
-        <v>57141</v>
+        <v>87412</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,49 +2472,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>3624</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Slåttmyren, Slåttmyren, Jmt</t>
+          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500910</v>
+        <v>500422</v>
       </c>
       <c r="R18" t="n">
-        <v>7025978</v>
+        <v>7026184</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2547,12 +2522,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2563,75 +2538,71 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Tallskog - barrblandskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Bodil Carlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115230124</t>
+          <t>https://artportalen.se/Sighting/1208310</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115230295</v>
+        <v>1208311</v>
       </c>
       <c r="B19" t="n">
-        <v>58114</v>
+        <v>87412</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>3624</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Slåttmyren, Slåttmyren, Jmt</t>
+          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500700</v>
+        <v>500435</v>
       </c>
       <c r="R19" t="n">
-        <v>7026044</v>
+        <v>7026139</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2658,12 +2629,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,75 +2645,71 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Tallskog - barrblandskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Bodil Carlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115230295</t>
+          <t>https://artportalen.se/Sighting/1208311</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115230735</v>
+        <v>137527880</v>
       </c>
       <c r="B20" t="n">
-        <v>58114</v>
+        <v>87663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>3624</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Våttjärnen, Våttjärnen, Jmt</t>
+          <t>Slåttmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500399</v>
+        <v>500421</v>
       </c>
       <c r="R20" t="n">
-        <v>7026304</v>
+        <v>7026184</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2769,12 +2736,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2789,27 +2756,31 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115230735</t>
+          <t>https://artportalen.se/Sighting/137527880</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4899153</v>
+        <v>1256195</v>
       </c>
       <c r="B21" t="n">
-        <v>100143</v>
+        <v>89035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,23 +2788,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222467</v>
+        <v>4398</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Vitvaxing agg.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Hoppe</t>
-        </is>
-      </c>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2841,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500743</v>
+        <v>500716</v>
       </c>
       <c r="R21" t="n">
-        <v>7026479</v>
+        <v>7026420</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2879,6 +2846,11 @@
           <t>2012-09-10</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>äldre skogsbilvägskant, vid liten bäck</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2890,7 +2862,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Blandsumpskog - rikkärr</t>
+          <t>Tallskog - barrblandskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2911,38 +2883,38 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4899153</t>
+          <t>https://artportalen.se/Sighting/1256195</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4964589</v>
+        <v>1869486</v>
       </c>
       <c r="B22" t="n">
-        <v>101326</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2952,13 +2924,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500330</v>
+        <v>500519</v>
       </c>
       <c r="R22" t="n">
-        <v>7026347</v>
+        <v>7026330</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2992,7 +2964,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>på och vid gammal basväg</t>
+          <t>sparsamt på ett par granar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,51 +2999,51 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4964589</t>
+          <t>https://artportalen.se/Sighting/1869486</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4964590</v>
+        <v>137527982</v>
       </c>
       <c r="B23" t="n">
-        <v>101326</v>
+        <v>79539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+          <t>Slåttmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500392</v>
+        <v>500735</v>
       </c>
       <c r="R23" t="n">
-        <v>7026375</v>
+        <v>7026456</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3108,7 +3080,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>vid Källbäcken</t>
+          <t>sparsamt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,16 +3091,11 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Tallskog - barrblandskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bodil Carlsson</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -3138,56 +3105,56 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>Åtgärdsprogram för hotade arter</t>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4964590</t>
+          <t>https://artportalen.se/Sighting/137527982</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4964591</v>
+        <v>137527983</v>
       </c>
       <c r="B24" t="n">
-        <v>101326</v>
+        <v>79539</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+          <t>Slåttmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500396</v>
+        <v>500518</v>
       </c>
       <c r="R24" t="n">
-        <v>7026360</v>
+        <v>7026329</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3224,7 +3191,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>nära Källbäcken</t>
+          <t>sparsamt på ett par granar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3235,16 +3202,11 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Tallskog - barrblandskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bodil Carlsson</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -3254,59 +3216,64 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>Åtgärdsprogram för hotade arter</t>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4964591</t>
+          <t>https://artportalen.se/Sighting/137527983</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>91488972</v>
+        <v>115229281</v>
       </c>
       <c r="B25" t="n">
-        <v>101326</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Slåttmyren, Slåttmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500601</v>
+        <v>501010</v>
       </c>
       <c r="R25" t="n">
-        <v>7026377</v>
+        <v>7026103</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3330,12 +3297,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3350,22 +3322,3932 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115229281</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>115229440</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>501041</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7026164</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115229440</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>115229743</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>500980</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7026149</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115229743</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>115230124</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>500910</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7025978</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115230124</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>115230295</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>500700</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7026044</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115230295</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>115230735</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Våttjärnen, Våttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>500399</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7026304</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115230735</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137527981</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58142</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>500448</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7026128</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527981</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137527942</v>
+      </c>
+      <c r="B32" t="n">
+        <v>108480</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>500433</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7026123</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527942</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137527943</v>
+      </c>
+      <c r="B33" t="n">
+        <v>108480</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>500441</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7026157</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527943</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137527944</v>
+      </c>
+      <c r="B34" t="n">
+        <v>108480</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>500421</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7026184</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527944</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137527945</v>
+      </c>
+      <c r="B35" t="n">
+        <v>108480</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>500414</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7026225</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527945</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137527946</v>
+      </c>
+      <c r="B36" t="n">
+        <v>108480</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>500396</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7026293</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527946</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137527947</v>
+      </c>
+      <c r="B37" t="n">
+        <v>108480</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>500395</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7026359</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>nära Källbäcken</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527947</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137527948</v>
+      </c>
+      <c r="B38" t="n">
+        <v>108480</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>500329</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7026347</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>på och vid gammal basväg</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527948</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137527949</v>
+      </c>
+      <c r="B39" t="n">
+        <v>108480</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>500276</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7026295</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527949</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137527951</v>
+      </c>
+      <c r="B40" t="n">
+        <v>108480</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>500722</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7026469</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527951</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137527952</v>
+      </c>
+      <c r="B41" t="n">
+        <v>108480</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>500717</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7026490</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527952</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137527923</v>
+      </c>
+      <c r="B42" t="n">
+        <v>108550</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>500717</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7026490</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527923</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137527931</v>
+      </c>
+      <c r="B43" t="n">
+        <v>110427</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220294</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Fjällskära</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Saussurea alpina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) DC.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>500405</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7026337</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527931</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137527933</v>
+      </c>
+      <c r="B44" t="n">
+        <v>110427</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220294</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Fjällskära</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Saussurea alpina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) DC.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>500717</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7026490</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527933</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137527868</v>
+      </c>
+      <c r="B45" t="n">
+        <v>106628</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>500231</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7026306</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527868</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137527870</v>
+      </c>
+      <c r="B46" t="n">
+        <v>106628</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>500687</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7026462</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527870</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4899153</v>
+      </c>
+      <c r="B47" t="n">
+        <v>100143</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>500743</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7026479</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Blandsumpskog - rikkärr</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4899153</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>137527929</v>
+      </c>
+      <c r="B48" t="n">
+        <v>100465</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>500742</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7026479</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527929</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4964589</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>500330</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7026347</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>på och vid gammal basväg</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Tallskog - barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4964589</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4964590</v>
+      </c>
+      <c r="B50" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>500392</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7026375</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>vid Källbäcken</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Tallskog - barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4964590</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>4964591</v>
+      </c>
+      <c r="B51" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Slåttmyren / N /, norr om Örån, ca 1 km norr om Strangellsbodarna,, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>500396</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7026360</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>nära Källbäcken</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Tallskog - barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4964591</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>91488972</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>500601</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7026377</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AX52" t="inlineStr">
         <is>
           <t>Via Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr">
+      <c r="AY52" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/91488972</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137527953</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101654</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>500395</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7026359</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>nära Källbäcken</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527953</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>137527954</v>
+      </c>
+      <c r="B54" t="n">
+        <v>101654</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>500392</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7026374</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>vid Källbäcken</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527954</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>137527955</v>
+      </c>
+      <c r="B55" t="n">
+        <v>101654</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>500329</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7026347</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>på och vid gammal basväg</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527955</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>137527957</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101052</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>500520</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7026309</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527957</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>137527958</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101052</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>500392</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7026374</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>vid Källbäcken</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527958</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>137527959</v>
+      </c>
+      <c r="B58" t="n">
+        <v>101052</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>500302</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7026352</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527959</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>137527922</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99716</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>500392</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7026374</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>vid Källbäcken</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527922</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>137527864</v>
+      </c>
+      <c r="B60" t="n">
+        <v>103127</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>223037</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Humleblomster</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Geum rivale</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>500717</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7026490</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527864</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>137527920</v>
+      </c>
+      <c r="B61" t="n">
+        <v>101544</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Slåttmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>500329</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7026347</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2012-09-10</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>på och vid gammal basväg</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137527920</t>
         </is>
       </c>
     </row>
@@ -3395,6 +7277,42 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
